--- a/astro-site/public/dl/guia-churreria-chocolateria/carta-de-apertura-y-escandallo-churro.xlsx
+++ b/astro-site/public/dl/guia-churreria-chocolateria/carta-de-apertura-y-escandallo-churro.xlsx
@@ -2720,7 +2720,7 @@
       </c>
       <c r="I31" s="43">
         <f>SUM(I7:I30)</f>
-        <v>187.85207091230538</v>
+        <v>187.8520709123054</v>
       </c>
     </row>
     <row r="32"/>
@@ -8768,8 +8768,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="2">
+    <mergeCell ref="F61:N61"/>
     <mergeCell ref="G13:L14"/>
-    <mergeCell ref="F61:N61"/>
   </mergeCells>
   <dataValidations count="91">
     <dataValidation sqref="B13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fuera de rango" error="Escribe un valor entre 0 y 1." type="decimal" operator="between">
@@ -9528,8 +9528,8 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="3">
     <mergeCell ref="D20:G20"/>
+    <mergeCell ref="D19:G19"/>
     <mergeCell ref="A33:E33"/>
-    <mergeCell ref="D19:G19"/>
   </mergeCells>
   <conditionalFormatting sqref="E27">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
@@ -10125,11 +10125,11 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="5">
+    <mergeCell ref="B24:G24"/>
     <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C20:G20"/>
     <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C20:G20"/>
     <mergeCell ref="A29:G29"/>
-    <mergeCell ref="B24:G24"/>
   </mergeCells>
   <conditionalFormatting sqref="B24">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
@@ -10922,11 +10922,11 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="6">
     <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:E18"/>
     <mergeCell ref="A22:K22"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B20:E20"/>
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B20:E20"/>
   </mergeCells>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -14145,8 +14145,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="3">
+    <mergeCell ref="A42:N42"/>
     <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A42:N42"/>
     <mergeCell ref="B12:G12"/>
   </mergeCells>
   <conditionalFormatting sqref="B12">
@@ -14721,9 +14721,9 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="4">
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="B18:D18"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B18:D18"/>
   </mergeCells>
   <conditionalFormatting sqref="B20">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
